--- a/output/pdf_financials_xlsx/CNO.xlsx
+++ b/output/pdf_financials_xlsx/CNO.xlsx
@@ -1465,7 +1465,7 @@
         <v>-0.004044</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.763356</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>-0.168896</v>
@@ -1724,7 +1724,7 @@
         <v>0.079764</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.381678</v>
+        <v>-0.381678</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>-0.158333</v>
@@ -1919,7 +1919,7 @@
         <v>0.079764</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0.381678</v>
+        <v>-0.381678</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>-0.158333</v>
@@ -2463,7 +2463,7 @@
         <v>4.825315005727377</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>1598.939695162359</v>
@@ -2528,7 +2528,7 @@
         <v>5.771910959568257</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>11.43619228652234</v>
+        <v>-11.43619228652234</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>-2.543609064349375</v>
@@ -49211,10 +49211,10 @@
         </is>
       </c>
       <c r="T390" s="5" t="n">
-        <v>0.381678</v>
+        <v>-0.381678</v>
       </c>
       <c r="U390" s="5" t="n">
-        <v>0.381678</v>
+        <v>-0.381678</v>
       </c>
       <c r="V390" t="inlineStr">
         <is>
@@ -50898,10 +50898,10 @@
         </is>
       </c>
       <c r="S406" s="5" t="n">
-        <v>0.079764</v>
+        <v>-0.079764</v>
       </c>
       <c r="T406" s="5" t="n">
-        <v>0.079764</v>
+        <v>-0.079764</v>
       </c>
       <c r="U406" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CNO.xlsx
+++ b/output/pdf_financials_xlsx/CNO.xlsx
@@ -992,31 +992,31 @@
         <v>0.124067</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.09843200000000001</v>
+        <v>0.428879</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.08420900000000001</v>
+        <v>0.48257</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.098787</v>
+        <v>0.509962</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.137101</v>
+        <v>0.581427</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.066799</v>
+        <v>0.547334</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.12259</v>
+        <v>0.808922</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.310684</v>
+        <v>1.699335</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.635063</v>
+        <v>3.209829</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.659884</v>
+        <v>3.495475</v>
       </c>
     </row>
     <row r="11">
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         <v>-0.530922</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.301565</v>
+        <v>-0.304165</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.325671</v>
@@ -2303,7 +2303,7 @@
         <v>-0.530922</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.301565</v>
+        <v>-0.304165</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.325671</v>
@@ -2368,7 +2368,7 @@
         <v>-203.1832898332198</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-80.7444019909982</v>
+        <v>-81.44055520896646</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>-92.48443783083809</v>
@@ -2554,55 +2554,55 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.019985</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.005818</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.026967</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.005235</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.004234</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.185089</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.108687</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.018257</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.036192</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.018563</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.041951</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.019973</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.051332</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.216041</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.841352</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.533845</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.207182</v>
       </c>
     </row>
     <row r="35">
@@ -2676,55 +2676,55 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.019985</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.005818</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.026967</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.005235</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.004234</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.185089</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.108687</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.018257</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.036192</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.018563</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.041951</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.019973</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.051332</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.216041</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.841352</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.533845</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.207182</v>
       </c>
     </row>
     <row r="37">
@@ -3408,55 +3408,55 @@
         <v>0.0025</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.023081</v>
+        <v>0.003096</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.009832</v>
+        <v>0.004014</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.030781</v>
+        <v>0.003814</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.038818</v>
+        <v>0.033583</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.01346</v>
+        <v>0.009226</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.198631</v>
+        <v>0.013542</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.116169</v>
+        <v>0.007482</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.088278</v>
+        <v>0.070021</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.056112</v>
+        <v>0.01992</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.026657</v>
+        <v>0.008094</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.049398</v>
+        <v>0.007447</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.022486</v>
+        <v>0.002513</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.054225</v>
+        <v>0.002893</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.364189</v>
+        <v>0.148148</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.559564</v>
+        <v>0.718212</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.597542</v>
+        <v>0.063697</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.286405</v>
+        <v>0.079223</v>
       </c>
     </row>
     <row r="49">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -18826,7 +18826,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -44628,7 +44628,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -45132,7 +45132,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -47658,7 +47658,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -49870,7 +49870,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -52470,7 +52470,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -55402,7 +55402,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -61938,7 +61938,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -64246,7 +64246,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -64352,7 +64352,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -66680,7 +66680,7 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
